--- a/West_Group_Driver_Allocation_Report.xlsx
+++ b/West_Group_Driver_Allocation_Report.xlsx
@@ -180,8 +180,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M451" headerRowCount="1">
-  <autoFilter ref="A1:M451"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M449" headerRowCount="1">
+  <autoFilter ref="A1:M449"/>
   <tableColumns count="13">
     <tableColumn id="1" name="Driverid"/>
     <tableColumn id="2" name="Identity/reference"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M451"/>
+  <dimension ref="A1:M449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19774,16 +19774,14 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
-        <v>3611</v>
-      </c>
-      <c r="B349" s="2" t="inlineStr">
-        <is>
-          <t>CB6139501</t>
-        </is>
+        <v>3621</v>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>2489032538</v>
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>Noor Wahab Badam Sher</t>
+          <t>Umar Said</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -19791,42 +19789,58 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="E349" s="3" t="n"/>
+      <c r="E349" s="4" t="n">
+        <v>45992</v>
+      </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>WAITING FOR TRUCKS</t>
-        </is>
-      </c>
-      <c r="H349" s="2" t="n"/>
-      <c r="I349" s="3" t="n"/>
-      <c r="J349" s="2" t="n"/>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>Truck254</t>
+        </is>
+      </c>
+      <c r="I349" s="3" t="inlineStr">
+        <is>
+          <t>J T A 4951</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr">
+        <is>
+          <t>In Operation</t>
+        </is>
+      </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
-          <t>Out Of Operation</t>
-        </is>
-      </c>
-      <c r="L349" s="2" t="n"/>
-      <c r="M349" s="5" t="n">
-        <v>0</v>
+          <t>In Operation</t>
+        </is>
+      </c>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>West Co</t>
+        </is>
+      </c>
+      <c r="M349" s="6" t="n">
+        <v>1.1265</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
-        <v>3612</v>
-      </c>
-      <c r="B350" s="2" t="inlineStr">
-        <is>
-          <t>QY2743931</t>
-        </is>
+        <v>6200</v>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>2575539420</v>
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>Habib Ullah Musa Khan</t>
+          <t>Mahesh Kumar</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -19834,15 +19848,17 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="E350" s="3" t="n"/>
+      <c r="E350" s="4" t="n">
+        <v>45992</v>
+      </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>NEW DRIVERS</t>
+          <t>WAITING FOR TRUCKS</t>
         </is>
       </c>
       <c r="H350" s="2" t="n"/>
@@ -19860,14 +19876,14 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
-        <v>3621</v>
+        <v>6201</v>
       </c>
       <c r="B351" s="2" t="n">
-        <v>2489032538</v>
+        <v>2432776892</v>
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>Umar Said</t>
+          <t>Muhammad Nadeem</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -19885,48 +19901,32 @@
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
-        </is>
-      </c>
-      <c r="H351" s="2" t="inlineStr">
-        <is>
-          <t>Truck254</t>
-        </is>
-      </c>
-      <c r="I351" s="3" t="inlineStr">
-        <is>
-          <t>J T A 4951</t>
-        </is>
-      </c>
-      <c r="J351" s="2" t="inlineStr">
-        <is>
-          <t>In Operation</t>
-        </is>
-      </c>
+          <t>VACATION</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="n"/>
+      <c r="I351" s="3" t="n"/>
+      <c r="J351" s="2" t="n"/>
       <c r="K351" s="2" t="inlineStr">
         <is>
-          <t>In Operation</t>
-        </is>
-      </c>
-      <c r="L351" s="2" t="inlineStr">
-        <is>
-          <t>West Co</t>
-        </is>
-      </c>
-      <c r="M351" s="6" t="n">
-        <v>1.1265</v>
+          <t>Out Of Operation</t>
+        </is>
+      </c>
+      <c r="L351" s="2" t="n"/>
+      <c r="M351" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
-        <v>6200</v>
+        <v>6202</v>
       </c>
       <c r="B352" s="2" t="n">
-        <v>2575539420</v>
+        <v>2518318635</v>
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>Mahesh Kumar</t>
+          <t>Asad Ali</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -19944,32 +19944,48 @@
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>WAITING FOR TRUCKS</t>
-        </is>
-      </c>
-      <c r="H352" s="2" t="n"/>
-      <c r="I352" s="3" t="n"/>
-      <c r="J352" s="2" t="n"/>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>Truck253</t>
+        </is>
+      </c>
+      <c r="I352" s="3" t="inlineStr">
+        <is>
+          <t>J T A 4950</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr">
+        <is>
+          <t>In Operation</t>
+        </is>
+      </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
-          <t>Out Of Operation</t>
-        </is>
-      </c>
-      <c r="L352" s="2" t="n"/>
-      <c r="M352" s="5" t="n">
-        <v>0</v>
+          <t>In Operation</t>
+        </is>
+      </c>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>West Co</t>
+        </is>
+      </c>
+      <c r="M352" s="6" t="n">
+        <v>1.245</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
-        <v>6201</v>
+        <v>6203</v>
       </c>
       <c r="B353" s="2" t="n">
-        <v>2432776892</v>
+        <v>2532327570</v>
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Nadeem</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -19982,12 +19998,12 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>VACATION</t>
+          <t>WAITING FOR TRUCKS</t>
         </is>
       </c>
       <c r="H353" s="2" t="n"/>
@@ -20005,14 +20021,14 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
-        <v>6202</v>
+        <v>6204</v>
       </c>
       <c r="B354" s="2" t="n">
-        <v>2518318635</v>
+        <v>2432911473</v>
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>Asad Ali</t>
+          <t>Muhammad Israr</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -20021,7 +20037,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>45992</v>
+        <v>46142</v>
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
@@ -20035,12 +20051,12 @@
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>Truck253</t>
+          <t>Truck367</t>
         </is>
       </c>
       <c r="I354" s="3" t="inlineStr">
         <is>
-          <t>J T A 4950</t>
+          <t>H X A 2520</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -20059,19 +20075,19 @@
         </is>
       </c>
       <c r="M354" s="6" t="n">
-        <v>1.245</v>
+        <v>1.1582</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
-        <v>6203</v>
+        <v>8290</v>
       </c>
       <c r="B355" s="2" t="n">
-        <v>2532327570</v>
+        <v>2616425118</v>
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Shakeel Nazar Gull</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -20080,41 +20096,57 @@
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>45992</v>
+        <v>46098</v>
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>WAITING FOR TRUCKS</t>
-        </is>
-      </c>
-      <c r="H355" s="2" t="n"/>
-      <c r="I355" s="3" t="n"/>
-      <c r="J355" s="2" t="n"/>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>Truck231</t>
+        </is>
+      </c>
+      <c r="I355" s="3" t="inlineStr">
+        <is>
+          <t>J T A 4890</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr">
+        <is>
+          <t>In Operation</t>
+        </is>
+      </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
-          <t>Out Of Operation</t>
-        </is>
-      </c>
-      <c r="L355" s="2" t="n"/>
+          <t>In Operation</t>
+        </is>
+      </c>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>West Co</t>
+        </is>
+      </c>
       <c r="M355" s="5" t="n">
-        <v>0</v>
+        <v>0.8982</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
-        <v>6204</v>
+        <v>8291</v>
       </c>
       <c r="B356" s="2" t="n">
-        <v>2432911473</v>
+        <v>2610840981</v>
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Israr</t>
+          <t>Rahid Gul Shah Jee Gul</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -20123,26 +20155,26 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>46142</v>
+        <v>46098</v>
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>Truck367</t>
+          <t>Truck232</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>H X A 2520</t>
+          <t>J T A 4891</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr">
@@ -20160,20 +20192,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M356" s="6" t="n">
-        <v>1.1582</v>
+      <c r="M356" s="5" t="n">
+        <v>0.5004999999999999</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
-        <v>8290</v>
+        <v>8292</v>
       </c>
       <c r="B357" s="2" t="n">
-        <v>2616425118</v>
+        <v>2486925999</v>
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>Shakeel Nazar Gull</t>
+          <t>Asghar Khan Said Ali</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -20196,12 +20228,12 @@
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>Truck231</t>
+          <t>Truck239</t>
         </is>
       </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>J T A 4890</t>
+          <t>J T A 4898</t>
         </is>
       </c>
       <c r="J357" s="2" t="inlineStr">
@@ -20220,19 +20252,19 @@
         </is>
       </c>
       <c r="M357" s="5" t="n">
-        <v>0.8982</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
-        <v>8291</v>
+        <v>8293</v>
       </c>
       <c r="B358" s="2" t="n">
-        <v>2610840981</v>
+        <v>2542063595</v>
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>Rahid Gul Shah Jee Gul</t>
+          <t>Salman Khan</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -20245,22 +20277,22 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>Truck232</t>
+          <t>Truck227</t>
         </is>
       </c>
       <c r="I358" s="3" t="inlineStr">
         <is>
-          <t>J T A 4891</t>
+          <t>J T A 4885</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr">
@@ -20279,19 +20311,19 @@
         </is>
       </c>
       <c r="M358" s="5" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8013</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
-        <v>8292</v>
+        <v>8294</v>
       </c>
       <c r="B359" s="2" t="n">
-        <v>2486925999</v>
+        <v>2620283347</v>
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>Asghar Khan Said Ali</t>
+          <t>Waheed Murad Daud Khan</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -20304,22 +20336,22 @@
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>Truck239</t>
+          <t>Truck236</t>
         </is>
       </c>
       <c r="I359" s="3" t="inlineStr">
         <is>
-          <t>J T A 4898</t>
+          <t>J T A 4895</t>
         </is>
       </c>
       <c r="J359" s="2" t="inlineStr">
@@ -20338,19 +20370,19 @@
         </is>
       </c>
       <c r="M359" s="5" t="n">
-        <v>0.9782</v>
+        <v>0.8618</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
-        <v>8293</v>
+        <v>8295</v>
       </c>
       <c r="B360" s="2" t="n">
-        <v>2542063595</v>
+        <v>2515749071</v>
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>Salman Khan</t>
+          <t>Nazir Muhammad Pir Muhammad</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -20363,22 +20395,22 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>Truck227</t>
+          <t>Truck238</t>
         </is>
       </c>
       <c r="I360" s="3" t="inlineStr">
         <is>
-          <t>J T A 4885</t>
+          <t>J T A 4897</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
@@ -20397,19 +20429,19 @@
         </is>
       </c>
       <c r="M360" s="5" t="n">
-        <v>0.8013</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
-        <v>8294</v>
+        <v>8296</v>
       </c>
       <c r="B361" s="2" t="n">
-        <v>2620283347</v>
+        <v>2595160892</v>
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>Waheed Murad Daud Khan</t>
+          <t>Muhammad Bilal</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -20422,22 +20454,22 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>Truck236</t>
+          <t>Truck235</t>
         </is>
       </c>
       <c r="I361" s="3" t="inlineStr">
         <is>
-          <t>J T A 4895</t>
+          <t>J T A 4894</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
@@ -20456,19 +20488,19 @@
         </is>
       </c>
       <c r="M361" s="5" t="n">
-        <v>0.8618</v>
+        <v>0.6206</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
-        <v>8295</v>
+        <v>8297</v>
       </c>
       <c r="B362" s="2" t="n">
-        <v>2515749071</v>
+        <v>2594191617</v>
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>Nazir Muhammad Pir Muhammad</t>
+          <t>Hamid Khan Shaheen Khan</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -20481,22 +20513,22 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>Truck238</t>
+          <t>Truck230</t>
         </is>
       </c>
       <c r="I362" s="3" t="inlineStr">
         <is>
-          <t>J T A 4897</t>
+          <t>J T A 4889</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr">
@@ -20514,20 +20546,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M362" s="5" t="n">
-        <v>0.7289</v>
+      <c r="M362" s="6" t="n">
+        <v>1.081</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
-        <v>8296</v>
+        <v>8298</v>
       </c>
       <c r="B363" s="2" t="n">
-        <v>2595160892</v>
+        <v>2593430941</v>
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Bilal</t>
+          <t>Shohaib Khan</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -20550,12 +20582,12 @@
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>Truck235</t>
+          <t>Truck246</t>
         </is>
       </c>
       <c r="I363" s="3" t="inlineStr">
         <is>
-          <t>J T A 4894</t>
+          <t>J T A 4942</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr">
@@ -20574,19 +20606,19 @@
         </is>
       </c>
       <c r="M363" s="5" t="n">
-        <v>0.6206</v>
+        <v>0.7587</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
-        <v>8297</v>
+        <v>8299</v>
       </c>
       <c r="B364" s="2" t="n">
-        <v>2594191617</v>
+        <v>2595646312</v>
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>Hamid Khan Shaheen Khan</t>
+          <t>Abid Gul Niamat Gul</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -20599,22 +20631,22 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>Truck230</t>
+          <t>Truck240</t>
         </is>
       </c>
       <c r="I364" s="3" t="inlineStr">
         <is>
-          <t>J T A 4889</t>
+          <t>J T A 4936</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr">
@@ -20632,20 +20664,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M364" s="6" t="n">
-        <v>1.081</v>
+      <c r="M364" s="5" t="n">
+        <v>0.6348</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
-        <v>8298</v>
+        <v>8300</v>
       </c>
       <c r="B365" s="2" t="n">
-        <v>2593430941</v>
+        <v>2551468040</v>
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>Shohaib Khan</t>
+          <t>Afrasiyab Aslam Khan</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -20658,22 +20690,22 @@
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>Truck246</t>
+          <t>Truck234</t>
         </is>
       </c>
       <c r="I365" s="3" t="inlineStr">
         <is>
-          <t>J T A 4942</t>
+          <t>J T A 4893</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
@@ -20692,19 +20724,19 @@
         </is>
       </c>
       <c r="M365" s="5" t="n">
-        <v>0.7587</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
-        <v>8299</v>
+        <v>8301</v>
       </c>
       <c r="B366" s="2" t="n">
-        <v>2595646312</v>
+        <v>2619698067</v>
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>Abid Gul Niamat Gul</t>
+          <t>Kamran Gul Inam Gul</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -20717,22 +20749,22 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>Truck240</t>
+          <t>Truck228</t>
         </is>
       </c>
       <c r="I366" s="3" t="inlineStr">
         <is>
-          <t>J T A 4936</t>
+          <t>J T A 4886</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
@@ -20751,19 +20783,19 @@
         </is>
       </c>
       <c r="M366" s="5" t="n">
-        <v>0.6348</v>
+        <v>0.8057</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
-        <v>8300</v>
+        <v>8302</v>
       </c>
       <c r="B367" s="2" t="n">
-        <v>2551468040</v>
+        <v>2598776439</v>
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>Afrasiyab Aslam Khan</t>
+          <t>Fazal Amin</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -20776,22 +20808,22 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>Truck234</t>
+          <t>Truck354</t>
         </is>
       </c>
       <c r="I367" s="3" t="inlineStr">
         <is>
-          <t>J T A 4893</t>
+          <t>U T A 2447</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr">
@@ -20810,19 +20842,19 @@
         </is>
       </c>
       <c r="M367" s="5" t="n">
-        <v>0.862</v>
+        <v>0.6778999999999999</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
-        <v>8301</v>
+        <v>8303</v>
       </c>
       <c r="B368" s="2" t="n">
-        <v>2619698067</v>
+        <v>2605185582</v>
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>Kamran Gul Inam Gul</t>
+          <t>Manzor Islam</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -20835,22 +20867,22 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>Truck228</t>
+          <t>Truck366</t>
         </is>
       </c>
       <c r="I368" s="3" t="inlineStr">
         <is>
-          <t>J T A 4886</t>
+          <t>U T A 2531</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -20869,19 +20901,19 @@
         </is>
       </c>
       <c r="M368" s="5" t="n">
-        <v>0.8057</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
-        <v>8302</v>
+        <v>8304</v>
       </c>
       <c r="B369" s="2" t="n">
-        <v>2598776439</v>
+        <v>2608340705</v>
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>Fazal Amin</t>
+          <t>Rashid Khan Nazar Khan</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -20894,22 +20926,22 @@
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>Truck354</t>
+          <t>Truck237</t>
         </is>
       </c>
       <c r="I369" s="3" t="inlineStr">
         <is>
-          <t>U T A 2447</t>
+          <t>J T A 4896</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -20927,20 +20959,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M369" s="5" t="n">
-        <v>0.6778999999999999</v>
+      <c r="M369" s="6" t="n">
+        <v>1.0063</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
-        <v>8303</v>
+        <v>8305</v>
       </c>
       <c r="B370" s="2" t="n">
-        <v>2605185582</v>
+        <v>2525773723</v>
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>Manzor Islam</t>
+          <t>Zeeshan Shafaras</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -20963,12 +20995,12 @@
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>Truck366</t>
+          <t>Truck203</t>
         </is>
       </c>
       <c r="I370" s="3" t="inlineStr">
         <is>
-          <t>U T A 2531</t>
+          <t>A T A 6437</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
@@ -20986,20 +21018,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M370" s="5" t="n">
-        <v>0.664</v>
+      <c r="M370" s="6" t="n">
+        <v>1.0079</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
-        <v>8304</v>
+        <v>8306</v>
       </c>
       <c r="B371" s="2" t="n">
-        <v>2608340705</v>
+        <v>2506154216</v>
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>Rashid Khan Nazar Khan</t>
+          <t>Wali Ullah</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -21012,22 +21044,22 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>Truck237</t>
+          <t>Truck204</t>
         </is>
       </c>
       <c r="I371" s="3" t="inlineStr">
         <is>
-          <t>J T A 4896</t>
+          <t>A T A 6493</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr">
@@ -21046,19 +21078,19 @@
         </is>
       </c>
       <c r="M371" s="6" t="n">
-        <v>1.0063</v>
+        <v>1.0672</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
-        <v>8305</v>
+        <v>8307</v>
       </c>
       <c r="B372" s="2" t="n">
-        <v>2525773723</v>
+        <v>2603840923</v>
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>Zeeshan Shafaras</t>
+          <t>Rafi Ullah</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -21081,12 +21113,12 @@
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>Truck203</t>
+          <t>Truck205</t>
         </is>
       </c>
       <c r="I372" s="3" t="inlineStr">
         <is>
-          <t>A T A 6437</t>
+          <t>A T A 6438</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr">
@@ -21110,14 +21142,14 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
-        <v>8306</v>
+        <v>8308</v>
       </c>
       <c r="B373" s="2" t="n">
-        <v>2506154216</v>
+        <v>2330653029</v>
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>Wali Ullah</t>
+          <t>Muhammad Khalid</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -21140,12 +21172,12 @@
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>Truck204</t>
+          <t>Truck202</t>
         </is>
       </c>
       <c r="I373" s="3" t="inlineStr">
         <is>
-          <t>A T A 6493</t>
+          <t>A T A 6363</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
@@ -21164,19 +21196,19 @@
         </is>
       </c>
       <c r="M373" s="6" t="n">
-        <v>1.0672</v>
+        <v>1.3043</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
-        <v>8307</v>
+        <v>8309</v>
       </c>
       <c r="B374" s="2" t="n">
-        <v>2603840923</v>
+        <v>2603844651</v>
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>Rafi Ullah</t>
+          <t>Muhammad Azam</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -21199,12 +21231,12 @@
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>Truck205</t>
+          <t>Truck209</t>
         </is>
       </c>
       <c r="I374" s="3" t="inlineStr">
         <is>
-          <t>A T A 6438</t>
+          <t>A X K 3499</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -21222,20 +21254,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M374" s="6" t="n">
-        <v>1.0079</v>
+      <c r="M374" s="5" t="n">
+        <v>0.6522</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
-        <v>8308</v>
+        <v>8310</v>
       </c>
       <c r="B375" s="2" t="n">
-        <v>2330653029</v>
+        <v>2599118151</v>
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Khalid</t>
+          <t>Sami Ullah</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -21258,12 +21290,12 @@
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>Truck202</t>
+          <t>Truck206</t>
         </is>
       </c>
       <c r="I375" s="3" t="inlineStr">
         <is>
-          <t>A T A 6363</t>
+          <t>A X K 3405</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -21282,19 +21314,19 @@
         </is>
       </c>
       <c r="M375" s="6" t="n">
-        <v>1.3043</v>
+        <v>1.0672</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
-        <v>8309</v>
+        <v>8316</v>
       </c>
       <c r="B376" s="2" t="n">
-        <v>2603844651</v>
+        <v>2613383245</v>
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Azam</t>
+          <t>Muhammad Amir</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -21303,26 +21335,26 @@
         </is>
       </c>
       <c r="E376" s="4" t="n">
-        <v>46098</v>
+        <v>46102</v>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>Truck209</t>
+          <t>Truck243</t>
         </is>
       </c>
       <c r="I376" s="3" t="inlineStr">
         <is>
-          <t>A X K 3499</t>
+          <t>J T A 4939</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr">
@@ -21341,19 +21373,19 @@
         </is>
       </c>
       <c r="M376" s="5" t="n">
-        <v>0.6522</v>
+        <v>0.8032</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
-        <v>8310</v>
+        <v>8317</v>
       </c>
       <c r="B377" s="2" t="n">
-        <v>2599118151</v>
+        <v>2603842135</v>
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>Sami Ullah</t>
+          <t>Bagh Jameen Khan</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -21362,26 +21394,26 @@
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>46098</v>
+        <v>46102</v>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>Truck206</t>
+          <t>Truck242</t>
         </is>
       </c>
       <c r="I377" s="3" t="inlineStr">
         <is>
-          <t>A X K 3405</t>
+          <t>J T A 4938</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
@@ -21399,20 +21431,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M377" s="6" t="n">
-        <v>1.0672</v>
+      <c r="M377" s="5" t="n">
+        <v>0.6891</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
-        <v>8316</v>
+        <v>8318</v>
       </c>
       <c r="B378" s="2" t="n">
-        <v>2613383245</v>
+        <v>2614802417</v>
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Amir</t>
+          <t>Shah Azam</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -21435,12 +21467,12 @@
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>Truck243</t>
+          <t>Truck247</t>
         </is>
       </c>
       <c r="I378" s="3" t="inlineStr">
         <is>
-          <t>J T A 4939</t>
+          <t>J T A 4943</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -21459,19 +21491,19 @@
         </is>
       </c>
       <c r="M378" s="5" t="n">
-        <v>0.8032</v>
+        <v>0.8022</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
-        <v>8317</v>
+        <v>8319</v>
       </c>
       <c r="B379" s="2" t="n">
-        <v>2603842135</v>
+        <v>2610729184</v>
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>Bagh Jameen Khan</t>
+          <t>Yousaf Khan</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -21484,22 +21516,22 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>Truck242</t>
+          <t>Truck248</t>
         </is>
       </c>
       <c r="I379" s="3" t="inlineStr">
         <is>
-          <t>J T A 4938</t>
+          <t>J T A 4944</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr">
@@ -21518,19 +21550,19 @@
         </is>
       </c>
       <c r="M379" s="5" t="n">
-        <v>0.6891</v>
+        <v>0.5266999999999999</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
-        <v>8318</v>
+        <v>8320</v>
       </c>
       <c r="B380" s="2" t="n">
-        <v>2614802417</v>
+        <v>2608779936</v>
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>Shah Azam</t>
+          <t>Khilwat Khan</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -21543,22 +21575,22 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>Truck247</t>
+          <t>Truck245</t>
         </is>
       </c>
       <c r="I380" s="3" t="inlineStr">
         <is>
-          <t>J T A 4943</t>
+          <t>J T A 4941</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
@@ -21576,20 +21608,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M380" s="5" t="n">
-        <v>0.8022</v>
+      <c r="M380" s="6" t="n">
+        <v>1.0188</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
-        <v>8319</v>
+        <v>8321</v>
       </c>
       <c r="B381" s="2" t="n">
-        <v>2610729184</v>
+        <v>2609651167</v>
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>Yousaf Khan</t>
+          <t>Muhammad Iqrar</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -21602,22 +21634,22 @@
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>Truck248</t>
+          <t>Truck250</t>
         </is>
       </c>
       <c r="I381" s="3" t="inlineStr">
         <is>
-          <t>J T A 4944</t>
+          <t>J T A 4946</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr">
@@ -21636,19 +21668,19 @@
         </is>
       </c>
       <c r="M381" s="5" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.7593</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
-        <v>8320</v>
+        <v>8338</v>
       </c>
       <c r="B382" s="2" t="n">
-        <v>2608779936</v>
+        <v>2594342772</v>
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>Khilwat Khan</t>
+          <t>Zabih Ullah Afridi</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -21657,26 +21689,26 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>46102</v>
+        <v>46122</v>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>Truck245</t>
+          <t>Truck241</t>
         </is>
       </c>
       <c r="I382" s="3" t="inlineStr">
         <is>
-          <t>J T A 4941</t>
+          <t>J T A 4937</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -21694,20 +21726,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M382" s="6" t="n">
-        <v>1.0188</v>
+      <c r="M382" s="5" t="n">
+        <v>0.8995</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
-        <v>8321</v>
+        <v>8339</v>
       </c>
       <c r="B383" s="2" t="n">
-        <v>2609651167</v>
+        <v>2603842424</v>
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Iqrar</t>
+          <t>Walid Khan</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -21716,7 +21748,7 @@
         </is>
       </c>
       <c r="E383" s="4" t="n">
-        <v>46102</v>
+        <v>46122</v>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
@@ -21730,12 +21762,12 @@
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>Truck250</t>
+          <t>Truck229</t>
         </is>
       </c>
       <c r="I383" s="3" t="inlineStr">
         <is>
-          <t>J T A 4946</t>
+          <t>J T A 4887</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -21754,19 +21786,19 @@
         </is>
       </c>
       <c r="M383" s="5" t="n">
-        <v>0.7593</v>
+        <v>0.8734</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
-        <v>8338</v>
+        <v>8340</v>
       </c>
       <c r="B384" s="2" t="n">
-        <v>2594342772</v>
+        <v>2603842564</v>
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>Zabih Ullah Afridi</t>
+          <t>Fazal Amin Khan</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -21779,22 +21811,22 @@
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>Truck241</t>
+          <t>Truck244</t>
         </is>
       </c>
       <c r="I384" s="3" t="inlineStr">
         <is>
-          <t>J T A 4937</t>
+          <t>J T A 4940</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -21813,19 +21845,19 @@
         </is>
       </c>
       <c r="M384" s="5" t="n">
-        <v>0.8995</v>
+        <v>0.9842</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
-        <v>8339</v>
+        <v>8341</v>
       </c>
       <c r="B385" s="2" t="n">
-        <v>2603842424</v>
+        <v>2598538144</v>
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>Walid Khan</t>
+          <t>Masood Khan</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -21838,22 +21870,20 @@
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
-        </is>
-      </c>
-      <c r="H385" s="2" t="inlineStr">
-        <is>
-          <t>Truck229</t>
-        </is>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="n">
+        <v>2161</v>
       </c>
       <c r="I385" s="3" t="inlineStr">
         <is>
-          <t>J T A 4887</t>
+          <t>N S A 6518</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr">
@@ -21872,19 +21902,21 @@
         </is>
       </c>
       <c r="M385" s="5" t="n">
-        <v>0.8734</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
-        <v>8340</v>
-      </c>
-      <c r="B386" s="2" t="n">
-        <v>2603842564</v>
+        <v>8347</v>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>MJ6905342</t>
+        </is>
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>Fazal Amin Khan</t>
+          <t>Aftab Hussain Iqbal Hussain</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -21893,7 +21925,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>46122</v>
+        <v>46140</v>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
@@ -21907,12 +21939,12 @@
       </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>Truck244</t>
+          <t>Truck016</t>
         </is>
       </c>
       <c r="I386" s="3" t="inlineStr">
         <is>
-          <t>J T A 4940</t>
+          <t>G R A 1464</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr">
@@ -21931,19 +21963,21 @@
         </is>
       </c>
       <c r="M386" s="5" t="n">
-        <v>0.9842</v>
+        <v>0.6006</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
-        <v>8341</v>
-      </c>
-      <c r="B387" s="2" t="n">
-        <v>2598538144</v>
+        <v>8348</v>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>TP9154631</t>
+        </is>
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>Masood Khan</t>
+          <t>Abdur Rehman Saeed Ahmad Ahmad</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -21952,24 +21986,26 @@
         </is>
       </c>
       <c r="E387" s="4" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
-        </is>
-      </c>
-      <c r="H387" s="2" t="n">
-        <v>2161</v>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>Truck049</t>
+        </is>
       </c>
       <c r="I387" s="3" t="inlineStr">
         <is>
-          <t>N S A 6518</t>
+          <t>J S A 7481</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr">
@@ -21988,21 +22024,21 @@
         </is>
       </c>
       <c r="M387" s="5" t="n">
-        <v>0.622</v>
+        <v>0.8109</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
-        <v>8347</v>
+        <v>8349</v>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>MJ6905342</t>
+          <t>TY4168921</t>
         </is>
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>Aftab Hussain Iqbal Hussain</t>
+          <t>Umar Khan Sher Gul</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -22011,7 +22047,7 @@
         </is>
       </c>
       <c r="E388" s="4" t="n">
-        <v>46140</v>
+        <v>46124</v>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
@@ -22025,12 +22061,12 @@
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>Truck016</t>
+          <t>Truck119</t>
         </is>
       </c>
       <c r="I388" s="3" t="inlineStr">
         <is>
-          <t>G R A 1464</t>
+          <t>Z X A 8898</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
@@ -22049,21 +22085,21 @@
         </is>
       </c>
       <c r="M388" s="5" t="n">
-        <v>0.6006</v>
+        <v>0.7005</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
-        <v>8348</v>
+        <v>8350</v>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>TP9154631</t>
+          <t>ME4792891</t>
         </is>
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>Abdur Rehman Saeed Ahmad Ahmad</t>
+          <t>Fahmeed Gul Sahib Gul</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -22086,12 +22122,12 @@
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>Truck049</t>
+          <t>Truck075</t>
         </is>
       </c>
       <c r="I389" s="3" t="inlineStr">
         <is>
-          <t>J S A 7481</t>
+          <t>N S A 6259</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
@@ -22110,21 +22146,21 @@
         </is>
       </c>
       <c r="M389" s="5" t="n">
-        <v>0.8109</v>
+        <v>0.6026</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
-        <v>8349</v>
+        <v>8351</v>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>TY4168921</t>
+          <t>BJ1862221</t>
         </is>
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>Umar Khan Sher Gul</t>
+          <t>Ismail Akhtar Hussain Hussain</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -22137,22 +22173,22 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>Truck119</t>
+          <t>Truck093</t>
         </is>
       </c>
       <c r="I390" s="3" t="inlineStr">
         <is>
-          <t>Z X A 8898</t>
+          <t>N S A 6277</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr">
@@ -22171,21 +22207,21 @@
         </is>
       </c>
       <c r="M390" s="5" t="n">
-        <v>0.7005</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
-        <v>8350</v>
+        <v>8352</v>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>ME4792891</t>
+          <t>TF1017091</t>
         </is>
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>Fahmeed Gul Sahib Gul</t>
+          <t>Muhammad Abbas Ijaz Ahmes</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -22198,22 +22234,22 @@
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JUBAIL/JUBAIL</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>Truck075</t>
+          <t>Truck097</t>
         </is>
       </c>
       <c r="I391" s="3" t="inlineStr">
         <is>
-          <t>N S A 6259</t>
+          <t>N S A 6281</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr">
@@ -22232,21 +22268,21 @@
         </is>
       </c>
       <c r="M391" s="5" t="n">
-        <v>0.6026</v>
+        <v>0.7691</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
-        <v>8351</v>
+        <v>8353</v>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>BJ1862221</t>
+          <t>UM1850931</t>
         </is>
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>Ismail Akhtar Hussain Hussain</t>
+          <t>Hazrat Ali Taj Gul</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -22264,17 +22300,17 @@
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
+          <t>JUBAIL/JUBAIL</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>Truck093</t>
+          <t>Truck054</t>
         </is>
       </c>
       <c r="I392" s="3" t="inlineStr">
         <is>
-          <t>N S A 6277</t>
+          <t>R S A 5008</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -22293,21 +22329,21 @@
         </is>
       </c>
       <c r="M392" s="5" t="n">
-        <v>0.8131</v>
+        <v>0.6126</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
-        <v>8352</v>
+        <v>8354</v>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>TF1017091</t>
+          <t>YN5143922</t>
         </is>
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Abbas Ijaz Ahmes</t>
+          <t>Sohail Shah Munawar Khan</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -22316,7 +22352,7 @@
         </is>
       </c>
       <c r="E393" s="4" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
@@ -22325,17 +22361,17 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>JUBAIL/JUBAIL</t>
+          <t>JUB - JED - JUB</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>Truck097</t>
+          <t>Truck083</t>
         </is>
       </c>
       <c r="I393" s="3" t="inlineStr">
         <is>
-          <t>N S A 6281</t>
+          <t>N S A 6267</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr">
@@ -22354,21 +22390,21 @@
         </is>
       </c>
       <c r="M393" s="5" t="n">
-        <v>0.7691</v>
+        <v>0.9046</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
-        <v>8353</v>
+        <v>8355</v>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>UM1850931</t>
+          <t>MS4150541</t>
         </is>
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>Hazrat Ali Taj Gul</t>
+          <t>Ajmal Khan Iqbal Khan</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -22377,26 +22413,26 @@
         </is>
       </c>
       <c r="E394" s="4" t="n">
-        <v>46124</v>
+        <v>46132</v>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>JUBAIL/JUBAIL</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>Truck054</t>
+          <t>Truck100</t>
         </is>
       </c>
       <c r="I394" s="3" t="inlineStr">
         <is>
-          <t>R S A 5008</t>
+          <t>N S A 6284</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr">
@@ -22415,21 +22451,21 @@
         </is>
       </c>
       <c r="M394" s="5" t="n">
-        <v>0.6126</v>
+        <v>0.2215</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
-        <v>8354</v>
+        <v>8356</v>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>YN5143922</t>
+          <t>ZN4154961</t>
         </is>
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>Sohail Shah Munawar Khan</t>
+          <t>Waqar Khan Pervez Khan</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -22438,26 +22474,24 @@
         </is>
       </c>
       <c r="E395" s="4" t="n">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>JUB - JED - JUB</t>
-        </is>
-      </c>
-      <c r="H395" s="2" t="inlineStr">
-        <is>
-          <t>Truck083</t>
-        </is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="n">
+        <v>2120</v>
       </c>
       <c r="I395" s="3" t="inlineStr">
         <is>
-          <t>N S A 6267</t>
+          <t>V D A 2677</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr">
@@ -22476,21 +22510,21 @@
         </is>
       </c>
       <c r="M395" s="5" t="n">
-        <v>0.9046</v>
+        <v>0.7667</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
-        <v>8355</v>
+        <v>8357</v>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>MS4150541</t>
+          <t>CV4715071</t>
         </is>
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>Ajmal Khan Iqbal Khan</t>
+          <t>Gulstan Gulzar Khan Khan</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -22513,12 +22547,12 @@
       </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
-          <t>Truck100</t>
+          <t>Truck361</t>
         </is>
       </c>
       <c r="I396" s="3" t="inlineStr">
         <is>
-          <t>N S A 6284</t>
+          <t>U T A 2508</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr">
@@ -22537,21 +22571,21 @@
         </is>
       </c>
       <c r="M396" s="5" t="n">
-        <v>0.2215</v>
+        <v>0.5672</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
-        <v>8356</v>
+        <v>8358</v>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>ZN4154961</t>
+          <t>SG1828142</t>
         </is>
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>Waqar Khan Pervez Khan</t>
+          <t>Nizar Ali Shamsher Ali</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -22572,12 +22606,14 @@
           <t>JED</t>
         </is>
       </c>
-      <c r="H397" s="2" t="n">
-        <v>2120</v>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>Truck195</t>
+        </is>
       </c>
       <c r="I397" s="3" t="inlineStr">
         <is>
-          <t>V D A 2677</t>
+          <t>Z X A 8767</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr">
@@ -22596,21 +22632,21 @@
         </is>
       </c>
       <c r="M397" s="5" t="n">
-        <v>0.7667</v>
+        <v>0.5824</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
-        <v>8357</v>
+        <v>8359</v>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>CV4715071</t>
+          <t>UN4165391</t>
         </is>
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>Gulstan Gulzar Khan Khan</t>
+          <t>Kamran Khan Zareen Khan</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -22623,22 +22659,22 @@
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>Truck361</t>
+          <t>Truck098</t>
         </is>
       </c>
       <c r="I398" s="3" t="inlineStr">
         <is>
-          <t>U T A 2508</t>
+          <t>N S A 6282</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr">
@@ -22657,21 +22693,21 @@
         </is>
       </c>
       <c r="M398" s="5" t="n">
-        <v>0.5672</v>
+        <v>0.4413</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>8358</v>
+        <v>8360</v>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>SG1828142</t>
+          <t>PF5194771</t>
         </is>
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>Nizar Ali Shamsher Ali</t>
+          <t>Muhammad Zohaib Hamayun Khan</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -22692,14 +22728,12 @@
           <t>JED</t>
         </is>
       </c>
-      <c r="H399" s="2" t="inlineStr">
-        <is>
-          <t>Truck195</t>
-        </is>
+      <c r="H399" s="2" t="n">
+        <v>2151</v>
       </c>
       <c r="I399" s="3" t="inlineStr">
         <is>
-          <t>Z X A 8767</t>
+          <t>V D A 3319</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr">
@@ -22718,21 +22752,21 @@
         </is>
       </c>
       <c r="M399" s="5" t="n">
-        <v>0.5824</v>
+        <v>0.6542</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>8359</v>
+        <v>8361</v>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>UN4165391</t>
+          <t>ES4140232</t>
         </is>
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>Kamran Khan Zareen Khan</t>
+          <t>Nisar Khan Said Rehman</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -22745,22 +22779,22 @@
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>Truck098</t>
+          <t>Truck359</t>
         </is>
       </c>
       <c r="I400" s="3" t="inlineStr">
         <is>
-          <t>N S A 6282</t>
+          <t>U T A 2484</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr">
@@ -22779,21 +22813,21 @@
         </is>
       </c>
       <c r="M400" s="5" t="n">
-        <v>0.4413</v>
+        <v>0.4381</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>8360</v>
+        <v>8362</v>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>PF5194771</t>
+          <t>RF4148372</t>
         </is>
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Zohaib Hamayun Khan</t>
+          <t>Sajid Khan Nishad Khan</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -22814,12 +22848,14 @@
           <t>JED</t>
         </is>
       </c>
-      <c r="H401" s="2" t="n">
-        <v>2151</v>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>Truck105</t>
+        </is>
       </c>
       <c r="I401" s="3" t="inlineStr">
         <is>
-          <t>V D A 3319</t>
+          <t>N S A 6447</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
@@ -22838,21 +22874,21 @@
         </is>
       </c>
       <c r="M401" s="5" t="n">
-        <v>0.6542</v>
+        <v>0.6726</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
-        <v>8361</v>
+        <v>8363</v>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>ES4140232</t>
+          <t>FN3705511</t>
         </is>
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>Nisar Khan Said Rehman</t>
+          <t>Muhammad Bilal Muhammad Tariq</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -22875,12 +22911,12 @@
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>Truck359</t>
+          <t>Truck362</t>
         </is>
       </c>
       <c r="I402" s="3" t="inlineStr">
         <is>
-          <t>U T A 2484</t>
+          <t>U T A 2521</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
@@ -22899,21 +22935,19 @@
         </is>
       </c>
       <c r="M402" s="5" t="n">
-        <v>0.4381</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>8362</v>
-      </c>
-      <c r="B403" s="2" t="inlineStr">
-        <is>
-          <t>RF4148372</t>
-        </is>
+        <v>8370</v>
+      </c>
+      <c r="B403" s="2" t="n">
+        <v>2625029356</v>
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>Sajid Khan Nishad Khan</t>
+          <t>Dawar Khan Shah</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -22922,26 +22956,26 @@
         </is>
       </c>
       <c r="E403" s="4" t="n">
-        <v>46132</v>
+        <v>46143</v>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>Truck105</t>
+          <t>Truck327</t>
         </is>
       </c>
       <c r="I403" s="3" t="inlineStr">
         <is>
-          <t>N S A 6447</t>
+          <t>U T A 2569</t>
         </is>
       </c>
       <c r="J403" s="2" t="inlineStr">
@@ -22960,21 +22994,19 @@
         </is>
       </c>
       <c r="M403" s="5" t="n">
-        <v>0.6726</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
-        <v>8363</v>
-      </c>
-      <c r="B404" s="2" t="inlineStr">
-        <is>
-          <t>FN3705511</t>
-        </is>
+        <v>8371</v>
+      </c>
+      <c r="B404" s="2" t="n">
+        <v>2609653346</v>
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Bilal Muhammad Tariq</t>
+          <t>Adnan Khan</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -22983,7 +23015,7 @@
         </is>
       </c>
       <c r="E404" s="4" t="n">
-        <v>46132</v>
+        <v>46143</v>
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
@@ -22997,12 +23029,12 @@
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>Truck362</t>
+          <t>Truck185</t>
         </is>
       </c>
       <c r="I404" s="3" t="inlineStr">
         <is>
-          <t>U T A 2521</t>
+          <t>H X A 3213</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
@@ -23021,19 +23053,19 @@
         </is>
       </c>
       <c r="M404" s="5" t="n">
-        <v>0.752</v>
+        <v>0.7959000000000001</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
-        <v>8370</v>
+        <v>8372</v>
       </c>
       <c r="B405" s="2" t="n">
-        <v>2625029356</v>
+        <v>2611636610</v>
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>Dawar Khan Shah</t>
+          <t>Muhammad Ibrar Muhammad Nawaz</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -23056,12 +23088,12 @@
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>Truck327</t>
+          <t>Truck326</t>
         </is>
       </c>
       <c r="I405" s="3" t="inlineStr">
         <is>
-          <t>U T A 2569</t>
+          <t>U T A 2568</t>
         </is>
       </c>
       <c r="J405" s="2" t="inlineStr">
@@ -23079,20 +23111,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M405" s="5" t="n">
-        <v>0.842</v>
+      <c r="M405" s="6" t="n">
+        <v>1.0099</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>8371</v>
+        <v>8373</v>
       </c>
       <c r="B406" s="2" t="n">
-        <v>2609653346</v>
+        <v>2611636396</v>
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>Adnan Khan</t>
+          <t>Muhammad Imtiaz Khan Zali</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -23115,12 +23147,12 @@
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>Truck185</t>
+          <t>Truck325</t>
         </is>
       </c>
       <c r="I406" s="3" t="inlineStr">
         <is>
-          <t>H X A 3213</t>
+          <t>U T A 2567</t>
         </is>
       </c>
       <c r="J406" s="2" t="inlineStr">
@@ -23138,20 +23170,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M406" s="5" t="n">
-        <v>0.7959000000000001</v>
+      <c r="M406" s="6" t="n">
+        <v>1.0115</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
-        <v>8372</v>
+        <v>8374</v>
       </c>
       <c r="B407" s="2" t="n">
-        <v>2611636610</v>
+        <v>2586325231</v>
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Ibrar Muhammad Nawaz</t>
+          <t>Muhammad Faisal Khalid Rehman</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
@@ -23174,12 +23206,12 @@
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>Truck326</t>
+          <t>Truck332</t>
         </is>
       </c>
       <c r="I407" s="3" t="inlineStr">
         <is>
-          <t>U T A 2568</t>
+          <t>U T A 2574</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
@@ -23197,20 +23229,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M407" s="6" t="n">
-        <v>1.0099</v>
+      <c r="M407" s="5" t="n">
+        <v>0.8656</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>8373</v>
+        <v>8375</v>
       </c>
       <c r="B408" s="2" t="n">
-        <v>2611636396</v>
+        <v>2627024561</v>
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Imtiaz Khan Zali</t>
+          <t>Hafeez Ullah Rabat Khan</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -23223,22 +23255,22 @@
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>Truck325</t>
+          <t>Truck039</t>
         </is>
       </c>
       <c r="I408" s="3" t="inlineStr">
         <is>
-          <t>U T A 2567</t>
+          <t>A S A 1964</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -23256,20 +23288,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M408" s="6" t="n">
-        <v>1.0115</v>
+      <c r="M408" s="5" t="n">
+        <v>0.4144</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
-        <v>8374</v>
+        <v>8376</v>
       </c>
       <c r="B409" s="2" t="n">
-        <v>2586325231</v>
+        <v>2585766203</v>
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Faisal Khalid Rehman</t>
+          <t>Noor Ali Zulhaider</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -23292,12 +23324,12 @@
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>Truck332</t>
+          <t>Truck337</t>
         </is>
       </c>
       <c r="I409" s="3" t="inlineStr">
         <is>
-          <t>U T A 2574</t>
+          <t>U T A 2617</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr">
@@ -23316,19 +23348,19 @@
         </is>
       </c>
       <c r="M409" s="5" t="n">
-        <v>0.8656</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>8375</v>
+        <v>8378</v>
       </c>
       <c r="B410" s="2" t="n">
-        <v>2627024561</v>
+        <v>2606019962</v>
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>Hafeez Ullah Rabat Khan</t>
+          <t>Shah Zeb Khan Jana S Khan</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -23341,22 +23373,22 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>Truck039</t>
+          <t>Truck342</t>
         </is>
       </c>
       <c r="I410" s="3" t="inlineStr">
         <is>
-          <t>A S A 1964</t>
+          <t>U T A 2622</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
@@ -23375,19 +23407,19 @@
         </is>
       </c>
       <c r="M410" s="5" t="n">
-        <v>0.4144</v>
+        <v>0.8053</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
-        <v>8376</v>
+        <v>8379</v>
       </c>
       <c r="B411" s="2" t="n">
-        <v>2585766203</v>
+        <v>2594304707</v>
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>Noor Ali Zulhaider</t>
+          <t>Abdul Wahid Guli Jan</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
@@ -23410,12 +23442,12 @@
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>Truck337</t>
+          <t>Truck334</t>
         </is>
       </c>
       <c r="I411" s="3" t="inlineStr">
         <is>
-          <t>U T A 2617</t>
+          <t>U T A 2576</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
@@ -23434,19 +23466,19 @@
         </is>
       </c>
       <c r="M411" s="5" t="n">
-        <v>0.9328</v>
+        <v>0.8260999999999999</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
-        <v>8378</v>
+        <v>8380</v>
       </c>
       <c r="B412" s="2" t="n">
-        <v>2606019962</v>
+        <v>2616292757</v>
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>Shah Zeb Khan Jana S Khan</t>
+          <t>Jehangir Murcha Khan</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -23459,22 +23491,22 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>JED</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>Truck342</t>
+          <t>Truck007</t>
         </is>
       </c>
       <c r="I412" s="3" t="inlineStr">
         <is>
-          <t>U T A 2622</t>
+          <t>G R A 1901</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
@@ -23493,19 +23525,19 @@
         </is>
       </c>
       <c r="M412" s="5" t="n">
-        <v>0.8053</v>
+        <v>0.5598</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
-        <v>8379</v>
+        <v>8381</v>
       </c>
       <c r="B413" s="2" t="n">
-        <v>2594304707</v>
+        <v>2622339394</v>
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>Abdul Wahid Guli Jan</t>
+          <t>Abdul Azeem Marwat Khan</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -23528,12 +23560,12 @@
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>Truck334</t>
+          <t>Truck339</t>
         </is>
       </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
-          <t>U T A 2576</t>
+          <t>U T A 2619</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr">
@@ -23552,19 +23584,21 @@
         </is>
       </c>
       <c r="M413" s="5" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.7203000000000001</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
-        <v>8380</v>
-      </c>
-      <c r="B414" s="2" t="n">
-        <v>2616292757</v>
+        <v>8383</v>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>BW6991691</t>
+        </is>
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>Jehangir Murcha Khan</t>
+          <t>Abu Huraira</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -23577,22 +23611,22 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
+          <t>JED - YAN</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>Truck007</t>
+          <t>Truck356</t>
         </is>
       </c>
       <c r="I414" s="3" t="inlineStr">
         <is>
-          <t>G R A 1901</t>
+          <t>U T A 2475</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -23611,19 +23645,19 @@
         </is>
       </c>
       <c r="M414" s="5" t="n">
-        <v>0.5598</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
-        <v>8381</v>
+        <v>8384</v>
       </c>
       <c r="B415" s="2" t="n">
-        <v>2622339394</v>
+        <v>2597544986</v>
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>Abdul Azeem Marwat Khan</t>
+          <t>Mehruban Shah Saidan Shah</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -23646,12 +23680,12 @@
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>Truck339</t>
+          <t>Truck335</t>
         </is>
       </c>
       <c r="I415" s="3" t="inlineStr">
         <is>
-          <t>U T A 2619</t>
+          <t>U T A 2615</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr">
@@ -23670,21 +23704,19 @@
         </is>
       </c>
       <c r="M415" s="5" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7909</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
-        <v>8383</v>
-      </c>
-      <c r="B416" s="2" t="inlineStr">
-        <is>
-          <t>BW6991691</t>
-        </is>
+        <v>8385</v>
+      </c>
+      <c r="B416" s="2" t="n">
+        <v>2622504161</v>
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>Abu Huraira</t>
+          <t>Wali Sher Ali</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
@@ -23707,12 +23739,12 @@
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>Truck356</t>
+          <t>Truck333</t>
         </is>
       </c>
       <c r="I416" s="3" t="inlineStr">
         <is>
-          <t>U T A 2475</t>
+          <t>U T A 2575</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
@@ -23731,19 +23763,19 @@
         </is>
       </c>
       <c r="M416" s="5" t="n">
-        <v>0.8065</v>
+        <v>0.9166</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>8384</v>
+        <v>8386</v>
       </c>
       <c r="B417" s="2" t="n">
-        <v>2597544986</v>
+        <v>2621753827</v>
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>Mehruban Shah Saidan Shah</t>
+          <t>Imam Ul Haq Munir Afzal</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -23766,12 +23798,12 @@
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>Truck335</t>
+          <t>Truck338</t>
         </is>
       </c>
       <c r="I417" s="3" t="inlineStr">
         <is>
-          <t>U T A 2615</t>
+          <t>U T A 2618</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr">
@@ -23790,19 +23822,19 @@
         </is>
       </c>
       <c r="M417" s="5" t="n">
-        <v>0.7909</v>
+        <v>0.6749000000000001</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>8385</v>
+        <v>8387</v>
       </c>
       <c r="B418" s="2" t="n">
-        <v>2622504161</v>
+        <v>2618688234</v>
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>Wali Sher Ali</t>
+          <t>Khadi Hussain Noor Khan</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -23825,12 +23857,12 @@
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>Truck333</t>
+          <t>Truck150</t>
         </is>
       </c>
       <c r="I418" s="3" t="inlineStr">
         <is>
-          <t>U T A 2575</t>
+          <t>H X A 3128</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -23849,19 +23881,19 @@
         </is>
       </c>
       <c r="M418" s="5" t="n">
-        <v>0.9166</v>
+        <v>0.8498</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>8386</v>
+        <v>8388</v>
       </c>
       <c r="B419" s="2" t="n">
-        <v>2621753827</v>
+        <v>2603102191</v>
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>Imam Ul Haq Munir Afzal</t>
+          <t>Muhammad Noor Adil Jan</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -23884,12 +23916,12 @@
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>Truck338</t>
+          <t>Truck331</t>
         </is>
       </c>
       <c r="I419" s="3" t="inlineStr">
         <is>
-          <t>U T A 2618</t>
+          <t>U T A 2573</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
@@ -23908,19 +23940,19 @@
         </is>
       </c>
       <c r="M419" s="5" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
-        <v>8387</v>
+        <v>8389</v>
       </c>
       <c r="B420" s="2" t="n">
-        <v>2618688234</v>
+        <v>2574342321</v>
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>Khadi Hussain Noor Khan</t>
+          <t>Aziz Ur Rehman Ashraf Khan</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -23943,12 +23975,12 @@
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>Truck150</t>
+          <t>Truck353</t>
         </is>
       </c>
       <c r="I420" s="3" t="inlineStr">
         <is>
-          <t>H X A 3128</t>
+          <t>U T A 2663</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr">
@@ -23967,19 +23999,19 @@
         </is>
       </c>
       <c r="M420" s="5" t="n">
-        <v>0.8498</v>
+        <v>0.5417</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
-        <v>8388</v>
+        <v>8390</v>
       </c>
       <c r="B421" s="2" t="n">
-        <v>2603102191</v>
+        <v>2603252962</v>
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Noor Adil Jan</t>
+          <t>Mustameen Sher Khel</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -23992,22 +24024,20 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
-        </is>
-      </c>
-      <c r="H421" s="2" t="inlineStr">
-        <is>
-          <t>Truck331</t>
-        </is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="n">
+        <v>2142</v>
       </c>
       <c r="I421" s="3" t="inlineStr">
         <is>
-          <t>U T A 2573</t>
+          <t>V D A 8804</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
@@ -24026,19 +24056,19 @@
         </is>
       </c>
       <c r="M421" s="5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.4765</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
-        <v>8389</v>
+        <v>8391</v>
       </c>
       <c r="B422" s="2" t="n">
-        <v>2574342321</v>
+        <v>2583186875</v>
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>Aziz Ur Rehman Ashraf Khan</t>
+          <t>Ajmal Khan Muhabat Khan</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -24061,12 +24091,12 @@
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>Truck353</t>
+          <t>Truck330</t>
         </is>
       </c>
       <c r="I422" s="3" t="inlineStr">
         <is>
-          <t>U T A 2663</t>
+          <t>U T A 2572</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr">
@@ -24085,19 +24115,19 @@
         </is>
       </c>
       <c r="M422" s="5" t="n">
-        <v>0.5417</v>
+        <v>0.9405</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
-        <v>8390</v>
+        <v>8392</v>
       </c>
       <c r="B423" s="2" t="n">
-        <v>2603252962</v>
+        <v>2525159451</v>
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>Mustameen Sher Khel</t>
+          <t>Muhammad Ibrahim Jalal Gul</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -24110,20 +24140,22 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
-        </is>
-      </c>
-      <c r="H423" s="2" t="n">
-        <v>2142</v>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>Truck329</t>
+        </is>
       </c>
       <c r="I423" s="3" t="inlineStr">
         <is>
-          <t>V D A 8804</t>
+          <t>U T A 2571</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -24142,19 +24174,19 @@
         </is>
       </c>
       <c r="M423" s="5" t="n">
-        <v>0.4765</v>
+        <v>0.7184</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
-        <v>8391</v>
+        <v>8393</v>
       </c>
       <c r="B424" s="2" t="n">
-        <v>2583186875</v>
+        <v>2560036598</v>
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>Ajmal Khan Muhabat Khan</t>
+          <t>Suliman Gul Abdul Majeed</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -24177,12 +24209,12 @@
       </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>Truck330</t>
+          <t>Truck252</t>
         </is>
       </c>
       <c r="I424" s="3" t="inlineStr">
         <is>
-          <t>U T A 2572</t>
+          <t>J T A 4948</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -24201,19 +24233,19 @@
         </is>
       </c>
       <c r="M424" s="5" t="n">
-        <v>0.9405</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>8392</v>
+        <v>8394</v>
       </c>
       <c r="B425" s="2" t="n">
-        <v>2525159451</v>
+        <v>2482681315</v>
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Ibrahim Jalal Gul</t>
+          <t>Nasir Khan Amir Zaman</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -24231,48 +24263,32 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
-        </is>
-      </c>
-      <c r="H425" s="2" t="inlineStr">
-        <is>
-          <t>Truck329</t>
-        </is>
-      </c>
-      <c r="I425" s="3" t="inlineStr">
-        <is>
-          <t>U T A 2571</t>
-        </is>
-      </c>
-      <c r="J425" s="2" t="inlineStr">
-        <is>
-          <t>In Operation</t>
-        </is>
-      </c>
+          <t>VACATION</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="n"/>
+      <c r="I425" s="3" t="n"/>
+      <c r="J425" s="2" t="n"/>
       <c r="K425" s="2" t="inlineStr">
         <is>
-          <t>In Operation</t>
-        </is>
-      </c>
-      <c r="L425" s="2" t="inlineStr">
-        <is>
-          <t>West Co</t>
-        </is>
-      </c>
+          <t>Out Of Operation</t>
+        </is>
+      </c>
+      <c r="L425" s="2" t="n"/>
       <c r="M425" s="5" t="n">
-        <v>0.7184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
-        <v>8393</v>
+        <v>8398</v>
       </c>
       <c r="B426" s="2" t="n">
-        <v>2560036598</v>
+        <v>2638023123</v>
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>Suliman Gul Abdul Majeed</t>
+          <t>Zia Ullah Shahzad Gul</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -24280,9 +24296,7 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="E426" s="4" t="n">
-        <v>46143</v>
-      </c>
+      <c r="E426" s="3" t="n"/>
       <c r="F426" s="2" t="inlineStr">
         <is>
           <t>Karimullah/Yanbu</t>
@@ -24295,12 +24309,12 @@
       </c>
       <c r="H426" s="2" t="inlineStr">
         <is>
-          <t>Truck252</t>
+          <t>Truck363</t>
         </is>
       </c>
       <c r="I426" s="3" t="inlineStr">
         <is>
-          <t>J T A 4948</t>
+          <t>U T A 2522</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr">
@@ -24319,19 +24333,19 @@
         </is>
       </c>
       <c r="M426" s="5" t="n">
-        <v>0.828</v>
+        <v>0.6146</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>8394</v>
+        <v>8399</v>
       </c>
       <c r="B427" s="2" t="n">
-        <v>2482681315</v>
+        <v>2638023024</v>
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>Nasir Khan Amir Zaman</t>
+          <t>Nabi Gul Taza Gul</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -24339,9 +24353,7 @@
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="E427" s="4" t="n">
-        <v>46143</v>
-      </c>
+      <c r="E427" s="3" t="n"/>
       <c r="F427" s="2" t="inlineStr">
         <is>
           <t>Karimullah/Yanbu</t>
@@ -24349,32 +24361,48 @@
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>VACATION</t>
-        </is>
-      </c>
-      <c r="H427" s="2" t="n"/>
-      <c r="I427" s="3" t="n"/>
-      <c r="J427" s="2" t="n"/>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>Truck360</t>
+        </is>
+      </c>
+      <c r="I427" s="3" t="inlineStr">
+        <is>
+          <t>U T A 2507</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>In Operation</t>
+        </is>
+      </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
-          <t>Out Of Operation</t>
-        </is>
-      </c>
-      <c r="L427" s="2" t="n"/>
+          <t>In Operation</t>
+        </is>
+      </c>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>West Co</t>
+        </is>
+      </c>
       <c r="M427" s="5" t="n">
-        <v>0</v>
+        <v>0.3468</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
-        <v>8398</v>
+        <v>8400</v>
       </c>
       <c r="B428" s="2" t="n">
-        <v>2638023123</v>
+        <v>2597550504</v>
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>Zia Ullah Shahzad Gul</t>
+          <t>Muhammad Shahid Khan Muh</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -24395,12 +24423,12 @@
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>Truck363</t>
+          <t>Truck225</t>
         </is>
       </c>
       <c r="I428" s="3" t="inlineStr">
         <is>
-          <t>U T A 2522</t>
+          <t>J T A 4883</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
@@ -24419,19 +24447,19 @@
         </is>
       </c>
       <c r="M428" s="5" t="n">
-        <v>0.6146</v>
+        <v>0.5808</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
-        <v>8399</v>
+        <v>8401</v>
       </c>
       <c r="B429" s="2" t="n">
-        <v>2638023024</v>
+        <v>2620722773</v>
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>Nabi Gul Taza Gul</t>
+          <t>Khan Alam Abdul Karim</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -24442,22 +24470,20 @@
       <c r="E429" s="3" t="n"/>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
-        </is>
-      </c>
-      <c r="H429" s="2" t="inlineStr">
-        <is>
-          <t>Truck360</t>
-        </is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="n">
+        <v>2065</v>
       </c>
       <c r="I429" s="3" t="inlineStr">
         <is>
-          <t>U T A 2507</t>
+          <t>A J A 1597</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr">
@@ -24475,20 +24501,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M429" s="5" t="n">
-        <v>0.3468</v>
+      <c r="M429" s="6" t="n">
+        <v>1.0636</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>8400</v>
+        <v>8402</v>
       </c>
       <c r="B430" s="2" t="n">
-        <v>2597550504</v>
+        <v>2572244214</v>
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Shahid Khan Muh</t>
+          <t>Refaqat Ullah Lal Shah</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -24509,12 +24535,12 @@
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>Truck225</t>
+          <t>Truck345</t>
         </is>
       </c>
       <c r="I430" s="3" t="inlineStr">
         <is>
-          <t>J T A 4883</t>
+          <t>U T A 2653</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr">
@@ -24533,19 +24559,19 @@
         </is>
       </c>
       <c r="M430" s="5" t="n">
-        <v>0.5808</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
-        <v>8401</v>
+        <v>8403</v>
       </c>
       <c r="B431" s="2" t="n">
-        <v>2620722773</v>
+        <v>2619022466</v>
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>Khan Alam Abdul Karim</t>
+          <t>Mumtaz Khan Jalat Khan</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -24556,20 +24582,22 @@
       <c r="E431" s="3" t="n"/>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
-        </is>
-      </c>
-      <c r="H431" s="2" t="n">
-        <v>2065</v>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>Truck328</t>
+        </is>
       </c>
       <c r="I431" s="3" t="inlineStr">
         <is>
-          <t>A J A 1597</t>
+          <t>U T A 2570</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -24587,20 +24615,20 @@
           <t>West Co</t>
         </is>
       </c>
-      <c r="M431" s="6" t="n">
-        <v>1.0636</v>
+      <c r="M431" s="5" t="n">
+        <v>0.9308</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>8402</v>
+        <v>8404</v>
       </c>
       <c r="B432" s="2" t="n">
-        <v>2572244214</v>
+        <v>2618292409</v>
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>Refaqat Ullah Lal Shah</t>
+          <t>Sahib Ullah Sawab Khan</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -24621,12 +24649,12 @@
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>Truck345</t>
+          <t>Truck341</t>
         </is>
       </c>
       <c r="I432" s="3" t="inlineStr">
         <is>
-          <t>U T A 2653</t>
+          <t>U T A 2621</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -24645,19 +24673,19 @@
         </is>
       </c>
       <c r="M432" s="5" t="n">
-        <v>0.9624</v>
+        <v>0.5613</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>8403</v>
+        <v>8405</v>
       </c>
       <c r="B433" s="2" t="n">
-        <v>2619022466</v>
+        <v>2627042720</v>
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>Mumtaz Khan Jalat Khan</t>
+          <t>Najeeb Ullah Ziwar Khan</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -24678,12 +24706,12 @@
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>Truck328</t>
+          <t>Truck336</t>
         </is>
       </c>
       <c r="I433" s="3" t="inlineStr">
         <is>
-          <t>U T A 2570</t>
+          <t>U T A 2616</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr">
@@ -24702,19 +24730,19 @@
         </is>
       </c>
       <c r="M433" s="5" t="n">
-        <v>0.9308</v>
+        <v>0.8844</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>8404</v>
+        <v>8406</v>
       </c>
       <c r="B434" s="2" t="n">
-        <v>2618292409</v>
+        <v>2627042563</v>
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>Sahib Ullah Sawab Khan</t>
+          <t>Muhammad Ismail Aman Khan</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -24725,22 +24753,20 @@
       <c r="E434" s="3" t="n"/>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
-        </is>
-      </c>
-      <c r="H434" s="2" t="inlineStr">
-        <is>
-          <t>Truck341</t>
-        </is>
+          <t>JED</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="n">
+        <v>2133</v>
       </c>
       <c r="I434" s="3" t="inlineStr">
         <is>
-          <t>U T A 2621</t>
+          <t>V D A 2679</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr">
@@ -24759,19 +24785,19 @@
         </is>
       </c>
       <c r="M434" s="5" t="n">
-        <v>0.5613</v>
+        <v>0.5019</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>8405</v>
+        <v>8410</v>
       </c>
       <c r="B435" s="2" t="n">
-        <v>2627042720</v>
+        <v>2602054195</v>
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>Najeeb Ullah Ziwar Khan</t>
+          <t>Said Wali Luqman Shah</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -24792,12 +24818,12 @@
       </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>Truck336</t>
+          <t>Truck343</t>
         </is>
       </c>
       <c r="I435" s="3" t="inlineStr">
         <is>
-          <t>U T A 2616</t>
+          <t>U T A 2623</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr">
@@ -24816,19 +24842,19 @@
         </is>
       </c>
       <c r="M435" s="5" t="n">
-        <v>0.8844</v>
+        <v>0.6052</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>8406</v>
+        <v>8411</v>
       </c>
       <c r="B436" s="2" t="n">
-        <v>2627042563</v>
+        <v>2603962305</v>
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>Muhammad Ismail Aman Khan</t>
+          <t>Mohammed Jehan</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -24839,20 +24865,22 @@
       <c r="E436" s="3" t="n"/>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karimullah/Yanbu</t>
         </is>
       </c>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>JED</t>
-        </is>
-      </c>
-      <c r="H436" s="2" t="n">
-        <v>2133</v>
+          <t>JED - YAN</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>Truck344</t>
+        </is>
       </c>
       <c r="I436" s="3" t="inlineStr">
         <is>
-          <t>V D A 2679</t>
+          <t>U T A 2652</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr">
@@ -24871,19 +24899,19 @@
         </is>
       </c>
       <c r="M436" s="5" t="n">
-        <v>0.5019</v>
+        <v>0.7043</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
-        <v>8410</v>
+        <v>8431</v>
       </c>
       <c r="B437" s="2" t="n">
-        <v>2602054195</v>
+        <v>2622303671</v>
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>Said Wali Luqman Shah</t>
+          <t>Akhtar Jan Naeem Jan</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -24904,12 +24932,12 @@
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>Truck343</t>
+          <t>Truck352</t>
         </is>
       </c>
       <c r="I437" s="3" t="inlineStr">
         <is>
-          <t>U T A 2623</t>
+          <t>U T A 2661</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr">
@@ -24928,19 +24956,19 @@
         </is>
       </c>
       <c r="M437" s="5" t="n">
-        <v>0.6052</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
-        <v>8411</v>
+        <v>8446</v>
       </c>
       <c r="B438" s="2" t="n">
-        <v>2603962305</v>
+        <v>2633948332</v>
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>Mohammed Jehan</t>
+          <t>Sabir Hayat Mirzad</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -24959,14 +24987,12 @@
           <t>JED - YAN</t>
         </is>
       </c>
-      <c r="H438" s="2" t="inlineStr">
-        <is>
-          <t>Truck344</t>
-        </is>
+      <c r="H438" s="2" t="n">
+        <v>2145</v>
       </c>
       <c r="I438" s="3" t="inlineStr">
         <is>
-          <t>U T A 2652</t>
+          <t>V D A 3322</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -24985,19 +25011,19 @@
         </is>
       </c>
       <c r="M438" s="5" t="n">
-        <v>0.7043</v>
+        <v>0.7469</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
-        <v>8431</v>
+        <v>8448</v>
       </c>
       <c r="B439" s="2" t="n">
-        <v>2622303671</v>
+        <v>2634629733</v>
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>Akhtar Jan Naeem Jan</t>
+          <t>Hakeem Khan Sherin Khan</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -25018,12 +25044,12 @@
       </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
-          <t>Truck352</t>
+          <t>Truck368</t>
         </is>
       </c>
       <c r="I439" s="3" t="inlineStr">
         <is>
-          <t>U T A 2661</t>
+          <t>H X A 2521</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr">
@@ -25042,19 +25068,19 @@
         </is>
       </c>
       <c r="M439" s="5" t="n">
-        <v>0.8469</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
-        <v>8446</v>
+        <v>8452</v>
       </c>
       <c r="B440" s="2" t="n">
-        <v>2633948332</v>
+        <v>2632190381</v>
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>Sabir Hayat Mirzad</t>
+          <t>Zahid Gul</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -25073,12 +25099,14 @@
           <t>JED - YAN</t>
         </is>
       </c>
-      <c r="H440" s="2" t="n">
-        <v>2145</v>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>Truck370</t>
+        </is>
       </c>
       <c r="I440" s="3" t="inlineStr">
         <is>
-          <t>V D A 3322</t>
+          <t>H X A 2516</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -25097,19 +25125,19 @@
         </is>
       </c>
       <c r="M440" s="5" t="n">
-        <v>0.7469</v>
+        <v>0.8789</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
-        <v>8448</v>
+        <v>8453</v>
       </c>
       <c r="B441" s="2" t="n">
-        <v>2634629733</v>
+        <v>2583445412</v>
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>Hakeem Khan Sherin Khan</t>
+          <t>Gul Naaim</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -25130,12 +25158,12 @@
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>Truck368</t>
+          <t>Truck371</t>
         </is>
       </c>
       <c r="I441" s="3" t="inlineStr">
         <is>
-          <t>H X A 2521</t>
+          <t>H X A 2517</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -25154,19 +25182,19 @@
         </is>
       </c>
       <c r="M441" s="5" t="n">
-        <v>0.9328</v>
+        <v>0.4713</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>8452</v>
+        <v>8455</v>
       </c>
       <c r="B442" s="2" t="n">
-        <v>2632190381</v>
+        <v>2634730648</v>
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>Zahid Gul</t>
+          <t>Shah Zaib Wakeel Khan</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -25187,12 +25215,12 @@
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>Truck370</t>
+          <t>Truck369</t>
         </is>
       </c>
       <c r="I442" s="3" t="inlineStr">
         <is>
-          <t>H X A 2516</t>
+          <t>H X A 2518</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -25211,121 +25239,89 @@
         </is>
       </c>
       <c r="M442" s="5" t="n">
-        <v>0.8789</v>
+        <v>0.8142</v>
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
-        <v>8453</v>
-      </c>
-      <c r="B443" s="2" t="n">
-        <v>2583445412</v>
-      </c>
-      <c r="C443" s="3" t="inlineStr">
-        <is>
-          <t>Gul Naaim</t>
-        </is>
-      </c>
-      <c r="D443" s="3" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
+      <c r="A443" s="2" t="n"/>
+      <c r="B443" s="2" t="n"/>
+      <c r="C443" s="3" t="n"/>
+      <c r="D443" s="3" t="n"/>
       <c r="E443" s="3" t="n"/>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>ACCIDENT</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>Truck371</t>
+          <t>Truck032</t>
         </is>
       </c>
       <c r="I443" s="3" t="inlineStr">
         <is>
-          <t>H X A 2517</t>
+          <t>U R A 4454</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
         <is>
-          <t>In Operation</t>
-        </is>
-      </c>
-      <c r="K443" s="2" t="inlineStr">
-        <is>
-          <t>In Operation</t>
-        </is>
-      </c>
+          <t>Out of Operation</t>
+        </is>
+      </c>
+      <c r="K443" s="2" t="n"/>
       <c r="L443" s="2" t="inlineStr">
         <is>
           <t>West Co</t>
         </is>
       </c>
       <c r="M443" s="5" t="n">
-        <v>0.4713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
-        <v>8455</v>
-      </c>
-      <c r="B444" s="2" t="n">
-        <v>2634730648</v>
-      </c>
-      <c r="C444" s="3" t="inlineStr">
-        <is>
-          <t>Shah Zaib Wakeel Khan</t>
-        </is>
-      </c>
-      <c r="D444" s="3" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
+      <c r="A444" s="2" t="n"/>
+      <c r="B444" s="2" t="n"/>
+      <c r="C444" s="3" t="n"/>
+      <c r="D444" s="3" t="n"/>
       <c r="E444" s="3" t="n"/>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>Karimullah/Yanbu</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>JED - YAN</t>
+          <t>ACCIDENT</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>Truck369</t>
+          <t>Truck068</t>
         </is>
       </c>
       <c r="I444" s="3" t="inlineStr">
         <is>
-          <t>H X A 2518</t>
+          <t>N S A 6252</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
         <is>
-          <t>In Operation</t>
-        </is>
-      </c>
-      <c r="K444" s="2" t="inlineStr">
-        <is>
-          <t>In Operation</t>
-        </is>
-      </c>
+          <t>Out of Operation</t>
+        </is>
+      </c>
+      <c r="K444" s="2" t="n"/>
       <c r="L444" s="2" t="inlineStr">
         <is>
           <t>West Co</t>
         </is>
       </c>
       <c r="M444" s="5" t="n">
-        <v>0.8142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -25346,12 +25342,12 @@
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>Truck032</t>
+          <t>Truck211</t>
         </is>
       </c>
       <c r="I445" s="3" t="inlineStr">
         <is>
-          <t>U R A 4454</t>
+          <t>D R A 3617</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr">
@@ -25377,7 +25373,7 @@
       <c r="E446" s="3" t="n"/>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>Alaa/Jeddah</t>
+          <t>Karim Awad/Jubail</t>
         </is>
       </c>
       <c r="G446" s="2" t="inlineStr">
@@ -25387,12 +25383,12 @@
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>Truck068</t>
+          <t>Truck251</t>
         </is>
       </c>
       <c r="I446" s="3" t="inlineStr">
         <is>
-          <t>N S A 6252</t>
+          <t>J T A 4947</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
@@ -25428,12 +25424,12 @@
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>Truck211</t>
+          <t>Truck207</t>
         </is>
       </c>
       <c r="I447" s="3" t="inlineStr">
         <is>
-          <t>D R A 3617</t>
+          <t>D R A 3614</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -25459,7 +25455,7 @@
       <c r="E448" s="3" t="n"/>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>Karim Awad/Jubail</t>
+          <t>Alaa/Jeddah</t>
         </is>
       </c>
       <c r="G448" s="2" t="inlineStr">
@@ -25469,12 +25465,12 @@
       </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>Truck251</t>
+          <t>Truck210</t>
         </is>
       </c>
       <c r="I448" s="3" t="inlineStr">
         <is>
-          <t>J T A 4947</t>
+          <t>D R A 3620</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -25510,12 +25506,12 @@
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>Truck207</t>
+          <t>Truck208</t>
         </is>
       </c>
       <c r="I449" s="3" t="inlineStr">
         <is>
-          <t>D R A 3614</t>
+          <t>D R A 3619</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -25530,88 +25526,6 @@
         </is>
       </c>
       <c r="M449" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" s="2" t="n"/>
-      <c r="B450" s="2" t="n"/>
-      <c r="C450" s="3" t="n"/>
-      <c r="D450" s="3" t="n"/>
-      <c r="E450" s="3" t="n"/>
-      <c r="F450" s="2" t="inlineStr">
-        <is>
-          <t>Alaa/Jeddah</t>
-        </is>
-      </c>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>ACCIDENT</t>
-        </is>
-      </c>
-      <c r="H450" s="2" t="inlineStr">
-        <is>
-          <t>Truck210</t>
-        </is>
-      </c>
-      <c r="I450" s="3" t="inlineStr">
-        <is>
-          <t>D R A 3620</t>
-        </is>
-      </c>
-      <c r="J450" s="2" t="inlineStr">
-        <is>
-          <t>Out of Operation</t>
-        </is>
-      </c>
-      <c r="K450" s="2" t="n"/>
-      <c r="L450" s="2" t="inlineStr">
-        <is>
-          <t>West Co</t>
-        </is>
-      </c>
-      <c r="M450" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" s="2" t="n"/>
-      <c r="B451" s="2" t="n"/>
-      <c r="C451" s="3" t="n"/>
-      <c r="D451" s="3" t="n"/>
-      <c r="E451" s="3" t="n"/>
-      <c r="F451" s="2" t="inlineStr">
-        <is>
-          <t>Alaa/Jeddah</t>
-        </is>
-      </c>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>ACCIDENT</t>
-        </is>
-      </c>
-      <c r="H451" s="2" t="inlineStr">
-        <is>
-          <t>Truck208</t>
-        </is>
-      </c>
-      <c r="I451" s="3" t="inlineStr">
-        <is>
-          <t>D R A 3619</t>
-        </is>
-      </c>
-      <c r="J451" s="2" t="inlineStr">
-        <is>
-          <t>Out of Operation</t>
-        </is>
-      </c>
-      <c r="K451" s="2" t="n"/>
-      <c r="L451" s="2" t="inlineStr">
-        <is>
-          <t>West Co</t>
-        </is>
-      </c>
-      <c r="M451" s="5" t="n">
         <v>0</v>
       </c>
     </row>
